--- a/artfynd/A 8998-2024 artfynd.xlsx
+++ b/artfynd/A 8998-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104147171</v>
+        <v>104147172</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>101410</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mjällån, nedanför Mjällåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623494.6177562692</v>
+        <v>623522</v>
       </c>
       <c r="R2" t="n">
-        <v>6951571.783331068</v>
+        <v>6951485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +748,14 @@
           <t>2022-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I naturligt dråg i ravin, ledningsgata</t>
+          <t>Gnagspår och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +769,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövrik granskog 50 - 60 år, örtrikt</t>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gamtall 70 cm i vägkant. Sannolikt en av områdets äldsta tallar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,6 +789,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering inför bildandet av naturreservaten Mjällådalen och Horten i Medelpad</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104147171</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mjällån, nedanför Mjällåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>623495</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6951572</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I naturligt dråg i ravin, ledningsgata</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lövrik granskog 50 - 60 år, örtrikt</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Inventering inför bildandet av naturreservaten Mjällådalen och Horten i Medelpad</t>
         </is>

--- a/artfynd/A 8998-2024 artfynd.xlsx
+++ b/artfynd/A 8998-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Inventering inför bildandet av naturreservaten Mjällådalen och Horten i Medelpad</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104147172</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
           <t>Inventering inför bildandet av naturreservaten Mjällådalen och Horten i Medelpad</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104147171</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>